--- a/reporte_productos.xlsx
+++ b/reporte_productos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,21 +466,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>cuido</t>
+          <t>champo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ña</t>
+          <t>trherh</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>56.00</t>
+          <t>200.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr"/>
     </row>
@@ -490,75 +490,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Juan David</t>
+          <t>login</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Para juano</t>
+          <t>dgfhbf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>56.00</t>
+          <t>10000.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>/static/uploads/triste.e7d7f861.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juguete </t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ia</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>56.00</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>45</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>kevin</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>abc</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>45</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>/static/uploads/login.png</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
